--- a/AY24-25/COD/ReportFormats/PGYR25OP_Format.xlsx
+++ b/AY24-25/COD/ReportFormats/PGYR25OP_Format.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertpatton/Repositories/FASolutions/FSADocumentation/AY23-24/COD/ReportFormats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertpatton/Repositories/FASolutions/FSADocumentation/AY24-25/COD/ReportFormats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93562E8-4C30-A74C-B8B9-3B8DF93D7942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{55A5347D-3B8A-4046-8C69-0819E4F128E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19620" yWindow="740" windowWidth="13980" windowHeight="20260" xr2:uid="{598557D2-139C-CF48-8435-AE8D090B2F2A}"/>
+    <workbookView xWindow="31800" yWindow="760" windowWidth="13980" windowHeight="20260" xr2:uid="{598557D2-139C-CF48-8435-AE8D090B2F2A}"/>
   </bookViews>
   <sheets>
-    <sheet name="PGYR24OP" sheetId="1" r:id="rId1"/>
+    <sheet name="PGYR25OP_Format" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
   <si>
     <t>Field #</t>
   </si>
@@ -65,9 +65,6 @@
     <t>CCYYMMDD</t>
   </si>
   <si>
-    <t>Filler1</t>
-  </si>
-  <si>
     <t>"D"</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>DisbursementDate</t>
   </si>
   <si>
-    <t>Filler2</t>
-  </si>
-  <si>
     <t>PaymentPeriodStartDate</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
     <t>TotalEligibilityUsedAcrossAllSchools</t>
   </si>
   <si>
-    <t>Filler3</t>
-  </si>
-  <si>
     <t>DisbursementProcessDate</t>
   </si>
   <si>
@@ -140,9 +131,6 @@
     <t>StudentFirstName</t>
   </si>
   <si>
-    <t>StudentMIddleInitial</t>
-  </si>
-  <si>
     <t>StudentSSN</t>
   </si>
   <si>
@@ -170,9 +158,6 @@
     <t>0000000, last 3 digits indicate less than 1 percent, no decimal point</t>
   </si>
   <si>
-    <t>ProgramCIPCode</t>
-  </si>
-  <si>
     <t>format is 00.0000 - 99.0000</t>
   </si>
   <si>
@@ -182,36 +167,18 @@
     <t>"F" = full-time, "Q" = three-quarters time, "H" = half-time, "L" = less than half-time</t>
   </si>
   <si>
-    <t>PublishedProgramLengthYears</t>
-  </si>
-  <si>
-    <t>PublishedProgramLengthMonths</t>
-  </si>
-  <si>
-    <t>PublishedProgramLengthWeeks</t>
-  </si>
-  <si>
     <t>00V000 to 99V000, or blank. Decimal is implied</t>
   </si>
   <si>
     <t>000V000 to 999V000, or blank. Decimal is implied</t>
   </si>
   <si>
-    <t>SpecialProgramIndicator</t>
-  </si>
-  <si>
     <t>"A" = Selective Admission Associate Program, "B" = Bachelor's Degree Completion Program, "N" = Not applicable, "P" = Preparatory Coursework Graduate Professional Program, "T" = Non-credential Teacher Certification Program, "U" = Prparatory Coursework Undergraduate Program</t>
   </si>
   <si>
-    <t>ProgramCredentialLevel</t>
-  </si>
-  <si>
     <t>01 = Undergraduate certificate or diploma, 02 = Associate degree, 03 = Bachelor's degree, 04 = Post Baccalaureate certificate</t>
   </si>
   <si>
-    <t>WeeksProgramsAcademicYear</t>
-  </si>
-  <si>
     <t>000V000 to 999V999, total number of weeks of instruction in the program's academic year</t>
   </si>
   <si>
@@ -231,6 +198,45 @@
   </si>
   <si>
     <t>Filler4</t>
+  </si>
+  <si>
+    <t>StudentSuffix</t>
+  </si>
+  <si>
+    <t>StudentMiddleName</t>
+  </si>
+  <si>
+    <t>ProgramCIPCode1</t>
+  </si>
+  <si>
+    <t>ProgramCIPCode2</t>
+  </si>
+  <si>
+    <t>ProgramCIPCode3</t>
+  </si>
+  <si>
+    <t>EnrollmentIntensityPercentage</t>
+  </si>
+  <si>
+    <t>0-100</t>
+  </si>
+  <si>
+    <t>PublishedProgramLengthYears1</t>
+  </si>
+  <si>
+    <t>PublishedProgramLengthMonths1</t>
+  </si>
+  <si>
+    <t>PublishedProgramLengthWeeks1</t>
+  </si>
+  <si>
+    <t>SpecialProgramIndicator1</t>
+  </si>
+  <si>
+    <t>ProgramCredentialLevel1</t>
+  </si>
+  <si>
+    <t>WeeksProgramsAcademicYear1</t>
   </si>
 </sst>
 </file>
@@ -604,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD6D0AB-361D-F74C-A0BB-96196AC7D46F}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -649,10 +655,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -663,13 +669,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -677,16 +683,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -694,19 +703,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -714,16 +720,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -731,16 +737,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -748,19 +757,19 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C8">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -768,10 +777,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C9">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -788,16 +797,19 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C10">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -805,19 +817,19 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
         <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -825,19 +837,19 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C12">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -845,19 +857,19 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C13">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -865,16 +877,19 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C14">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="D14">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -882,39 +897,34 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C15">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>26</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="C16">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -922,19 +932,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="C17">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -942,34 +949,33 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C18">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C19">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D19">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -977,16 +983,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C20">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -994,16 +1000,19 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C21">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1011,16 +1020,19 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="C22">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1028,19 +1040,19 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C23">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s">
         <v>36</v>
-      </c>
-      <c r="F23" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -1048,19 +1060,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C24">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
         <v>37</v>
-      </c>
-      <c r="F24" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1068,19 +1077,19 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C25">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
         <v>39</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1088,16 +1097,19 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C26">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>56</v>
+      </c>
+      <c r="F26" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1105,19 +1117,19 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="C27">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1125,19 +1137,19 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C28">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1145,19 +1157,19 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C29">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1165,19 +1177,19 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C30">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1185,19 +1197,19 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C31">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1205,19 +1217,19 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C32">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1225,19 +1237,19 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C33">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1245,19 +1257,19 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="C34">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1265,19 +1277,19 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C35">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1285,19 +1297,19 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C36">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1305,19 +1317,19 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C37">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1325,19 +1337,19 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C38">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1345,16 +1357,36 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C39">
+        <v>288</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>289</v>
+      </c>
+      <c r="C40">
         <v>350</v>
       </c>
-      <c r="D39">
-        <v>91</v>
-      </c>
-      <c r="E39" t="s">
-        <v>64</v>
+      <c r="D40">
+        <v>62</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
